--- a/assets/templates/match-result-upload-template.xlsx
+++ b/assets/templates/match-result-upload-template.xlsx
@@ -56,7 +56,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -67,15 +67,16 @@
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
     <col min="15" max="15" width="15" customWidth="1"/>
-    <col min="16" max="16" width="21" customWidth="1"/>
-    <col min="17" max="17" width="40" customWidth="1"/>
+    <col min="16" max="16" width="15" customWidth="1"/>
+    <col min="17" max="17" width="21" customWidth="1"/>
+    <col min="18" max="18" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -121,45 +122,50 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">score_model</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">played_on</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">table_label</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">format</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">duration_minutes</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">winning_camp</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">mvp_player_id</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">svp_player_id</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">scapegoat_player_id</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
@@ -204,43 +210,48 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">jingcheng_daily</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-04-08</t>
         </is>
       </c>
-      <c r="J2" s="0" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">A桌</t>
         </is>
       </c>
-      <c r="K2" s="0" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">经典十二人局</t>
         </is>
       </c>
-      <c r="L2" s="0">
+      <c r="M2" s="0">
         <v>60</v>
       </c>
-      <c r="M2" s="0" t="inlineStr">
+      <c r="N2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">villagers</t>
         </is>
       </c>
-      <c r="N2" s="0" t="inlineStr">
+      <c r="O2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">GZ-2026S-001</t>
         </is>
       </c>
-      <c r="O2" s="0" t="inlineStr">
+      <c r="P2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">GZ-2026S-007</t>
         </is>
       </c>
-      <c r="P2" s="0" t="inlineStr">
+      <c r="Q2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="Q2" s="0" t="inlineStr">
+      <c r="R2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">示例行，可直接覆盖；如果是编辑已有比赛，可将 import_mode 改为 update 并填写 match_id。</t>
         </is>
@@ -252,7 +263,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -263,8 +274,13 @@
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="19" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -305,15 +321,40 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">result_points</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vote_points</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">behavior_points</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">special_points</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">adjustment_points</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">points_earned</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">stance_result</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
@@ -354,14 +395,29 @@
         </is>
       </c>
       <c r="H2" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="I2" s="0" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="I2" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="J2" s="0">
+        <v>0</v>
+      </c>
+      <c r="K2" s="0">
+        <v>0</v>
+      </c>
+      <c r="L2" s="0">
+        <v>0</v>
+      </c>
+      <c r="M2" s="0">
+        <v>5.5</v>
+      </c>
+      <c r="N2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">correct</t>
         </is>
       </c>
-      <c r="J2" s="0" t="inlineStr">
+      <c r="O2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -402,14 +458,29 @@
         </is>
       </c>
       <c r="H3" s="0">
-        <v>2.5</v>
-      </c>
-      <c r="I3" s="0" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="I3" s="0">
+        <v>-0.5</v>
+      </c>
+      <c r="J3" s="0">
+        <v>0</v>
+      </c>
+      <c r="K3" s="0">
+        <v>0</v>
+      </c>
+      <c r="L3" s="0">
+        <v>0</v>
+      </c>
+      <c r="M3" s="0">
+        <v>4.5</v>
+      </c>
+      <c r="N3" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">correct</t>
         </is>
       </c>
-      <c r="J3" s="0" t="inlineStr">
+      <c r="O3" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -450,14 +521,29 @@
         </is>
       </c>
       <c r="H4" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="I4" s="0" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="I4" s="0">
+        <v>0</v>
+      </c>
+      <c r="J4" s="0">
+        <v>0</v>
+      </c>
+      <c r="K4" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="L4" s="0">
+        <v>0</v>
+      </c>
+      <c r="M4" s="0">
+        <v>5.5</v>
+      </c>
+      <c r="N4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">none</t>
         </is>
       </c>
-      <c r="J4" s="0" t="inlineStr">
+      <c r="O4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -498,14 +584,29 @@
         </is>
       </c>
       <c r="H5" s="0">
-        <v>1.5</v>
-      </c>
-      <c r="I5" s="0" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="I5" s="0">
+        <v>-1.0</v>
+      </c>
+      <c r="J5" s="0">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0">
+        <v>0</v>
+      </c>
+      <c r="L5" s="0">
+        <v>0</v>
+      </c>
+      <c r="M5" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="N5" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">none</t>
         </is>
       </c>
-      <c r="J5" s="0" t="inlineStr">
+      <c r="O5" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -546,14 +647,29 @@
         </is>
       </c>
       <c r="H6" s="0">
+        <v>5</v>
+      </c>
+      <c r="I6" s="0">
+        <v>0</v>
+      </c>
+      <c r="J6" s="0">
+        <v>0</v>
+      </c>
+      <c r="K6" s="0">
         <v>1.0</v>
       </c>
-      <c r="I6" s="0" t="inlineStr">
+      <c r="L6" s="0">
+        <v>0</v>
+      </c>
+      <c r="M6" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="N6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">incorrect</t>
         </is>
       </c>
-      <c r="J6" s="0" t="inlineStr">
+      <c r="O6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -594,14 +710,29 @@
         </is>
       </c>
       <c r="H7" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="I7" s="0" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="I7" s="0">
+        <v>0</v>
+      </c>
+      <c r="J7" s="0">
+        <v>0</v>
+      </c>
+      <c r="K7" s="0">
+        <v>0</v>
+      </c>
+      <c r="L7" s="0">
+        <v>0</v>
+      </c>
+      <c r="M7" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="N7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">none</t>
         </is>
       </c>
-      <c r="J7" s="0" t="inlineStr">
+      <c r="O7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -642,14 +773,29 @@
         </is>
       </c>
       <c r="H8" s="0">
-        <v>2.8</v>
-      </c>
-      <c r="I8" s="0" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="I8" s="0">
+        <v>0</v>
+      </c>
+      <c r="J8" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="K8" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="L8" s="0">
+        <v>0</v>
+      </c>
+      <c r="M8" s="0">
+        <v>7.5</v>
+      </c>
+      <c r="N8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">correct</t>
         </is>
       </c>
-      <c r="J8" s="0" t="inlineStr">
+      <c r="O8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">示例 SVP</t>
         </is>
@@ -690,14 +836,29 @@
         </is>
       </c>
       <c r="H9" s="0">
-        <v>0.8</v>
-      </c>
-      <c r="I9" s="0" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="I9" s="0">
+        <v>-0.5</v>
+      </c>
+      <c r="J9" s="0">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0">
+        <v>0</v>
+      </c>
+      <c r="L9" s="0">
+        <v>0</v>
+      </c>
+      <c r="M9" s="0">
+        <v>4.5</v>
+      </c>
+      <c r="N9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">none</t>
         </is>
       </c>
-      <c r="J9" s="0" t="inlineStr">
+      <c r="O9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -738,14 +899,29 @@
         </is>
       </c>
       <c r="H10" s="0">
-        <v>-0.5</v>
-      </c>
-      <c r="I10" s="0" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I10" s="0">
+        <v>0</v>
+      </c>
+      <c r="J10" s="0">
+        <v>0</v>
+      </c>
+      <c r="K10" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="L10" s="0">
+        <v>0</v>
+      </c>
+      <c r="M10" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="N10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">incorrect</t>
         </is>
       </c>
-      <c r="J10" s="0" t="inlineStr">
+      <c r="O10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -786,14 +962,29 @@
         </is>
       </c>
       <c r="H11" s="0">
+        <v>0</v>
+      </c>
+      <c r="I11" s="0">
+        <v>-0.5</v>
+      </c>
+      <c r="J11" s="0">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0">
+        <v>0</v>
+      </c>
+      <c r="L11" s="0">
+        <v>-0.5</v>
+      </c>
+      <c r="M11" s="0">
         <v>-1.0</v>
       </c>
-      <c r="I11" s="0" t="inlineStr">
+      <c r="N11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">incorrect</t>
         </is>
       </c>
-      <c r="J11" s="0" t="inlineStr">
+      <c r="O11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -834,14 +1025,29 @@
         </is>
       </c>
       <c r="H12" s="0">
-        <v>-1.5</v>
-      </c>
-      <c r="I12" s="0" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I12" s="0">
+        <v>0</v>
+      </c>
+      <c r="J12" s="0">
+        <v>-1.0</v>
+      </c>
+      <c r="K12" s="0">
+        <v>0</v>
+      </c>
+      <c r="L12" s="0">
+        <v>0</v>
+      </c>
+      <c r="M12" s="0">
+        <v>-1.0</v>
+      </c>
+      <c r="N12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">none</t>
         </is>
       </c>
-      <c r="J12" s="0" t="inlineStr">
+      <c r="O12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -882,14 +1088,29 @@
         </is>
       </c>
       <c r="H13" s="0">
-        <v>-2.0</v>
-      </c>
-      <c r="I13" s="0" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I13" s="0">
+        <v>0</v>
+      </c>
+      <c r="J13" s="0">
+        <v>0</v>
+      </c>
+      <c r="K13" s="0">
+        <v>-1.0</v>
+      </c>
+      <c r="L13" s="0">
+        <v>-0.5</v>
+      </c>
+      <c r="M13" s="0">
+        <v>-1.5</v>
+      </c>
+      <c r="N13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">incorrect</t>
         </is>
       </c>
-      <c r="J13" s="0" t="inlineStr">
+      <c r="O13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -901,7 +1122,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -968,12 +1189,12 @@
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">必填字段</t>
+          <t xml:space="preserve">score_model</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">competition_name、season_name、stage、round、game_no、played_on、table_label、format、duration_minutes、winning_camp、mvp_player_id、svp_player_id。</t>
+          <t xml:space="preserve">可填写 standard 或 jingcheng_daily；不填时默认按 standard 处理。</t>
         </is>
       </c>
     </row>
@@ -985,12 +1206,12 @@
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">winning_camp 取值</t>
+          <t xml:space="preserve">必填字段</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">只能填写 villagers 或 werewolves。</t>
+          <t xml:space="preserve">competition_name、season_name、stage、round、game_no、played_on、table_label、format、duration_minutes、winning_camp、mvp_player_id、svp_player_id。</t>
         </is>
       </c>
     </row>
@@ -1002,29 +1223,29 @@
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">背锅规则</t>
+          <t xml:space="preserve">winning_camp 取值</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">好人胜利时 scapegoat_player_id 留空；狼人胜利时必须填写，且要选失败阵营的选手。</t>
+          <t xml:space="preserve">只能填写 villagers 或 werewolves。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">players</t>
+          <t xml:space="preserve">matches</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">每场比赛需要 12 行</t>
+          <t xml:space="preserve">背锅规则</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">seat 建议填写 1 到 12；player_id 使用该赛季内的参赛 ID。数据库里不存在时，后续可以先按占位参赛 ID 录入。</t>
+          <t xml:space="preserve">好人胜利时 scapegoat_player_id 留空；狼人胜利时必须填写，且要选失败阵营的选手。</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1257,12 @@
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">camp 取值</t>
+          <t xml:space="preserve">每场比赛需要 12 行</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">当前模板按业务规则只保留 villagers / werewolves。</t>
+          <t xml:space="preserve">seat 建议填写 1 到 12；player_id 使用该赛季内的参赛 ID。数据库里不存在时，后续可以先按占位参赛 ID 录入。</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1274,12 @@
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">result 取值</t>
+          <t xml:space="preserve">camp 取值</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">只能填写 win 或 loss。</t>
+          <t xml:space="preserve">当前模板按业务规则只保留 villagers / werewolves。</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1291,12 @@
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">stance_result 取值</t>
+          <t xml:space="preserve">result 取值</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">填写 correct、incorrect 或 none；这个字段不是必填，不填时建议写 none。</t>
+          <t xml:space="preserve">只能填写 win 或 loss。</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1308,46 @@
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">stance_result 取值</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">填写 correct、incorrect 或 none；这个字段不是必填，不填时建议写 none。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">players</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">points_earned</t>
         </is>
       </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">支持整数或小数，模板示例使用一位小数。</t>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard 模型下必填总分；jingcheng_daily 模型下会按分项自动汇总，总分列可作为核对值保留。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">players</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">京城日报分项</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jingcheng_daily 模型支持填写 result_points、vote_points、behavior_points、special_points、adjustment_points。</t>
         </is>
       </c>
     </row>

--- a/assets/templates/match-result-upload-template.xlsx
+++ b/assets/templates/match-result-upload-template.xlsx
@@ -56,10 +56,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
@@ -254,6 +254,94 @@
       <c r="R2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">示例行，可直接覆盖；如果是编辑已有比赛，可将 import_mode 改为 update 并填写 match_id。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING-001</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">create</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAL广州公开赛</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026春季联赛</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">regular_season</t>
+        </is>
+      </c>
+      <c r="G3" s="0">
+        <v>1</v>
+      </c>
+      <c r="H3" s="0">
+        <v>2</v>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-09</t>
+        </is>
+      </c>
+      <c r="K3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B桌</t>
+        </is>
+      </c>
+      <c r="L3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">待补录</t>
+        </is>
+      </c>
+      <c r="M3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">示例待补录比赛：players 工作表可以先不填写，后续再到网站里补录。</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1210,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1211,7 +1299,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">competition_name、season_name、stage、round、game_no、played_on、table_label、format、duration_minutes、winning_camp、mvp_player_id、svp_player_id。</t>
+          <t xml:space="preserve">competition_name、season_name、stage、round、game_no、played_on、table_label、format 必填。正式比赛建议填写 duration_minutes、winning_camp、mvp_player_id、svp_player_id。</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1311,12 @@
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">winning_camp 取值</t>
+          <t xml:space="preserve">待补录比赛</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">只能填写 villagers 或 werewolves。</t>
+          <t xml:space="preserve">当 format 填写“待补录”时，可先留空 duration_minutes、winning_camp、MVP、SVP、背锅，也可以暂不填写 players 工作表。</t>
         </is>
       </c>
     </row>
@@ -1240,29 +1328,29 @@
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">背锅规则</t>
+          <t xml:space="preserve">winning_camp 取值</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">好人胜利时 scapegoat_player_id 留空；狼人胜利时必须填写，且要选失败阵营的选手。</t>
+          <t xml:space="preserve">正式比赛填写 villagers 或 werewolves；待补录比赛可留空，系统会按 draw 处理。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">players</t>
+          <t xml:space="preserve">matches</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">每场比赛需要 12 行</t>
+          <t xml:space="preserve">背锅规则</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">seat 建议填写 1 到 12；player_id 使用该赛季内的参赛 ID。数据库里不存在时，后续可以先按占位参赛 ID 录入。</t>
+          <t xml:space="preserve">好人胜利时 scapegoat_player_id 留空；狼人胜利时必须填写，且要选失败阵营的选手。</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1362,12 @@
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">camp 取值</t>
+          <t xml:space="preserve">每场比赛需要 12 行</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">当前模板按业务规则只保留 villagers / werewolves。</t>
+          <t xml:space="preserve">正式比赛建议填写完整 12 行；如果 matches.format=待补录，可以先不填 players 工作表，后续再在网站里补录。</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1379,12 @@
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">result 取值</t>
+          <t xml:space="preserve">camp 取值</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">只能填写 win 或 loss。</t>
+          <t xml:space="preserve">当前模板按业务规则只保留 villagers / werewolves。</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1396,12 @@
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">stance_result 取值</t>
+          <t xml:space="preserve">result 取值</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">填写 correct、incorrect 或 none；这个字段不是必填，不填时建议写 none。</t>
+          <t xml:space="preserve">只能填写 win 或 loss。</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1413,12 @@
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">points_earned</t>
+          <t xml:space="preserve">stance_result 取值</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">standard 模型下必填总分；jingcheng_daily 模型下会按分项自动汇总，总分列可作为核对值保留。</t>
+          <t xml:space="preserve">填写 correct、incorrect 或 none；这个字段不是必填，不填时建议写 none。</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1430,27 @@
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">points_earned</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard 模型下必填总分；jingcheng_daily 模型下会按分项自动汇总，总分列可作为核对值保留。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">players</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">京城日报分项</t>
         </is>
       </c>
-      <c r="C13" s="0" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">jingcheng_daily 模型支持填写 result_points、vote_points、behavior_points、special_points、adjustment_points。</t>
         </is>
